--- a/themes/yourRate.xlsx
+++ b/themes/yourRate.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,89 +450,69 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Подробная информация размещена на сайте по [ссылке](https://uralsib.ru/faq/personal/kredity/kredit-na-lyubye-tseli/usluga-svoya-stavka)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Подробная информация размещена на сайте по [ссылке](https://uralsib.ru/faq/personal/kredity/kredit-na-lyubye-tseli/usluga-svoya-stavka).</t>
+          <t xml:space="preserve">        Отказ от «Своей ставки» — возможен в течение 30 дней после подписания договора.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>сомнительное место: тире перед кратким прилагательным «возможен» («Отказ ... — возможен») формально не по правилу (тире между подлежащим и сказуемым ставится перед сущ./инф., а не перед кратким прилагательным). Может быть намеренным авторским тире для акцента — не стал убирать сам</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Отказ от «Своей ставки» — возможен в течение 30 дней после подписания договора.</t>
+          <t xml:space="preserve">        При отказе ставка увеличится: информация  — в п. 4 индивидуальных условий кредитного договора.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        При отказе ставка увеличится: информация — в п. 4 индивидуальных условий кредитного договора.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>сомнительное место: тире перед кратким прилагательным «возможен» («Отказ ... — возможен») формально не по правилу (тире между подлежащим и сказуемым ставится перед сущ./инф., а не перед кратким прилагательным). Может быть намеренным авторским тире для акцента — не стал убирать сам</t>
+          <t>убран двойной пробел</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        При отказе ставка увеличится: информация  — в п. 4 индивидуальных условий кредитного договора.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        При отказе ставка увеличится: информация — в п. 4 индивидуальных условий кредитного договора.</t>
+          <t xml:space="preserve">        Отказ от «Своей ставки» — возможен в течение 30 дней после подписания договора. </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>убран двойной пробел</t>
+          <t>то же сомнительное место, что и в блоке ConsumerLoan (стр. 34): тире перед кратким прилагательным «возможен»</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Отказ от «Своей ставки» — возможен в течение 30 дней после подписания договора. </t>
+          <t xml:space="preserve">        При отказе ставка увеличится: информация  — в п. 4 индивидуальных условий кредитного договора.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        При отказе ставка увеличится: информация — в п. 4 индивидуальных условий кредитного договора.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>то же сомнительное место, что и в блоке ConsumerLoan (стр. 34): тире перед кратким прилагательным «возможен»</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>45</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        При отказе ставка увеличится: информация  — в п. 4 индивидуальных условий кредитного договора.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        При отказе ставка увеличится: информация — в п. 4 индивидуальных условий кредитного договора.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
         <is>
           <t>убран двойной пробел</t>
         </is>
